--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2765,17 +2765,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Market conditions are currently stable.</t>
+          <t>Conduct a rapid feature gap analysis of Expedia's new back-office API and prioritize development of comparable or superior APIs within MONDEE's platform, targeting a 30‑day sprint to close the gap.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No high-priority competitor moves detected in this timeframe.</t>
+          <t>Launch a targeted marketing campaign that showcases MONDEE's existing back-office tools and upcoming enhancements, positioning the brand as a more integrated solution for travel operators.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Continue tracking standard sector intelligence.</t>
+          <t>Pursue a strategic partnership with a specialized back-office software provider to bundle complementary tools, enabling MONDEE to offer a comprehensive suite faster than competitors.</t>
         </is>
       </c>
     </row>
@@ -2819,17 +2819,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No competitor product launches or API releases cataloged.</t>
+          <t>Accelerate the development of a back‑office API that offers real‑time inventory and booking management, and release a beta version to our top 10 agency partners within 30 days to directly compete with Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Digital feature velocity remains normal.</t>
+          <t>Initiate a joint integration pilot with Expedia TAAP to demonstrate seamless interoperability, positioning MONDEE as the preferred partner for agencies that use both platforms and highlighting our unique data‑driven insights.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Continue monitoring competitor release notes.</t>
+          <t>Launch a targeted marketing campaign that showcases MONDEE’s existing back‑office automation features—such as faster processing times and lower costs—positioning them as superior to Expedia’s newly released tools for travel agencies seeking efficiency.</t>
         </is>
       </c>
     </row>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s features, prioritizing real‑time inventory, booking reference tools, and workflow automation to attract agencies seeking a seamless tech stack.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and promote it through targeted webinars to capture agency demand.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand and sell curated itineraries while integrating with MONDEE’s core platform, thereby expanding our partner ecosystem.</t>
+          <t>Create a Vancouver‑centric travel bundle that highlights the new car‑free Granville Street, using MONDEE’s data to offer exclusive itineraries and partner with local businesses for cross‑promotions.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a Vancouver‑centric travel package API that highlights the new pedestrian zone, offering curated walking tours and local experiences, and promote it to travel agencies to capitalize on the city’s increased foot traffic.</t>
+          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to provide agencies with a seamless, branded experience, and negotiate revenue‑share terms to expand market reach.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a dedicated back-office API suite for travel advisors, mirroring Expedia TAAP's features, and partner with a major agency network to pilot it within 90 days.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a sandbox for agencies to integrate and test, positioning MONDEE as the go‑to platform for agency automation. Prioritize API documentation and developer support to accelerate adoption among mid‑size agencies.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Leverage our existing white-label engine to create a co-branded travel platform for a mid-sized agency, offering integrated booking and analytics, to compete with Priceline Partner Network's quiet engine.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, enabling partners to brand and customize the booking experience, and target niche verticals such as corporate travel or experiential tours. Leverage existing data feeds to provide real‑time inventory and pricing, ensuring partners can compete with larger platforms.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Launch a targeted marketing campaign highlighting MONDEE's real-time data insights and AI-driven pricing tools, positioning us as the most efficient alternative to Expedia TAAP's new tools, and schedule a webinar for advisors within 30 days.</t>
+          <t>Collaborate with key travel advisors to pilot a new advisor‑centric feature set, including real‑time booking reference tools and workflow automation, and use the pilot data to refine the product roadmap. Publish case studies from early adopters to demonstrate ROI and attract additional agency clients.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop a dedicated back‑office API for travel advisors that includes real‑time inventory, commission tracking, and automated booking reference generation, directly addressing Expedia TAAP’s new toolset and positioning MONDEE as the preferred tech partner for agencies.</t>
+          <t>Launch a back‑office API suite for travel advisors that integrates booking, inventory, and commission management, mirroring Expedia TAAP, to retain agency partners and differentiate MONDEE’s platform. Develop a modular, developer‑friendly SDK that allows agencies to embed MONDEE’s core booking engine into their own portals within 90 days.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Launch a city‑partner program that provides travel advisors with a specialized API for pedestrian‑zone itineraries, using Vancouver’s Granville Street expansion as a pilot to showcase sustainable travel solutions and differentiate MONDEE’s offerings.</t>
+          <t>Partner with Vancouver city authorities to create a digital concierge service for the new Granville Street pedestrian zone, offering real‑time navigation, local business promotions, and exclusive offers to capture the increased foot traffic. Deploy a mobile app that aggregates local events, dining, and transport options, positioning MONDEE as the go‑to platform for downtown travelers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine similar to Priceline Partner Network’s model, and secure exclusive distribution agreements with mid‑market agencies to capture the growing demand for customizable booking platforms.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network, enabling third‑party agencies to brand MONDEE’s booking infrastructure and expand revenue streams. Offer a revenue‑share model and dedicated support to attract agencies looking to launch their own branded travel portals within 6 months.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors that includes booking reference generation and real‑time inventory access, mirroring Expedia TAAP’s new tools, and offer it as a free pilot to top 50 agencies.</t>
+          <t>Launch a dedicated back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s offerings, and open a beta program for agencies to test and provide feedback.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a rewards program for travel advisors that rewards higher booking volumes, directly competing with Expedia TAAP’s rewards, and integrate it into the API so advisors can track points in real time.</t>
+          <t>Form a strategic partnership with a leading travel agency network to embed MONDEE’s white‑label engine, positioning it as a direct competitor to Priceline Partner Network’s platform.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partner with a white‑label travel engine provider (e.g., Priceline Partner Network) to quickly roll out a customizable booking engine for agencies, positioning MONDEE as a one‑stop solution for agencies seeking both front‑end and back‑office capabilities.</t>
+          <t>Introduce a rewards program for advisors who book through MONDEE, offering tiered incentives and exclusive benefits to drive adoption and loyalty, similar to Expedia TAAP Rewards.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a back‑office API suite for travel agencies, offering a free pilot to the top 20 US advisors to secure early adoption and compete with Expedia TAAP’s new tools.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors that offers real‑time inventory, dynamic pricing, and AI‑driven recommendation engines, positioning MONDEE as a more efficient alternative to Expedia TAAP; pilot the API with a select group of boutique agencies within the next 90 days.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine that partners can brand, targeting mid‑market agencies currently using Expedia TAAP for back‑office solutions.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network’s model, enabling partners to brand and sell MONDEE’s inventory; secure a pilot partnership with a mid‑size OTA or corporate travel manager by the end of Q3.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a Vancouver‑centric travel package that highlights the new pedestrian zone, partnering with local businesses and influencers to capture the growing demand for walkable city experiences.</t>
+          <t>Capitalize on Vancouver’s new pedestrian zone by creating a curated “Granville Street Experience” travel package, partnering with local vendors and promoting it through social media influencers; launch the campaign within 60 days to capture early adopter interest.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference and inventory management, and promote it through a targeted outreach program to agencies using Expedia TAAP’s new tools.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a beta program to key agency partners within the next 60 days.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine on MONDEE’s platform and offer it as a plug‑in to mid‑market agencies, positioning it as a cost‑effective alternative to Priceline Partner Network’s engine.</t>
+          <t>Partner with a leading travel agency network to pilot a white‑label travel engine, leveraging MONDEE’s existing booking platform to capture the market segment targeted by Priceline Partner Network.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Develop an AI‑driven advisor assistant that automates itinerary creation and upsell suggestions, and integrate it into the new API to give agencies a competitive edge over Expedia’s standard offerings.</t>
+          <t>Introduce an automated booking reference management feature that integrates with our API, enabling agencies to streamline operations and compete directly with Expedia TAAP’s new booking reference tools.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API for travel advisors that offers real‑time inventory, booking reference tools, and automated commission calculations. Promote it via a webinar series targeting US travel agencies to counter Expedia TAAP’s new offerings.</t>
+          <t>Launch a dedicated back‑office API for travel advisors that offers real‑time inventory, booking reference, and commission tracking, directly addressing the new Expedia TAAP tools and positioning MONDEE as the preferred agency platform.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a 'Granville Street Experience' package that bundles local attractions, dining, and walking tours. Partner with Vancouver businesses to offer exclusive discounts, leveraging the new pedestrian zone to attract tourists.</t>
+          <t>Collaborate with Vancouver’s tourism authority to build a mobile app that highlights Granville Street’s pedestrian zone, offering dynamic routing, event schedules, and local vendor integrations, turning the positive expansion into a new revenue stream.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine focused on sustainability and local experiences. Pitch it to boutique agencies that want to differentiate from Priceline Partner Network’s generic engine.</t>
+          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s recommendation engine into their platform, ensuring visibility in the same ecosystem that hosts Expedia TAAP and countering the competitive advantage of their white‑label engine.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, integrating it into MONDEE’s existing advisor portal to streamline agency operations.</t>
+          <t>Develop and release a back‑office API suite for travel advisors, including real‑time booking reference tools, and initiate a pilot with top agencies to validate integration ease and gather feedback.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors that offers commission boosts and exclusive perks, directly addressing Expedia TAAP’s reward initiative and incentivizing partner loyalty.</t>
+          <t>Partner with a white‑label travel engine provider or build an in‑house engine to bundle with MONDEE’s platform, positioning it as a turnkey solution for agencies similar to Priceline Partner Network’s offering.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine similar to Priceline Partner Network, enabling agencies to brand and resell MONDEE’s inventory while maintaining control over the user experience.</t>
+          <t>Introduce a tiered rewards program for agencies that use MONDEE’s platform, mirroring Expedia TAAP Rewards, to incentivize higher booking volumes and strengthen loyalty.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors that offers real‑time inventory, dynamic pricing, and AI‑driven recommendation engines, positioning MONDEE as a more efficient alternative to Expedia TAAP; pilot the API with a select group of boutique agencies within the next 90 days.</t>
+          <t>Develop and release a back‑office API that allows travel advisors to manage bookings, reference numbers, and operational workflows directly within MONDEE, positioning it as a direct alternative to Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network’s model, enabling partners to brand and sell MONDEE’s inventory; secure a pilot partnership with a mid‑size OTA or corporate travel manager by the end of Q3.</t>
+          <t>Partner with Vancouver’s tourism authority to launch a mobile‑first itinerary and booking platform for the Granville Street car‑free zone, leveraging MONDEE’s data to capture the surge in local travel demand.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Capitalize on Vancouver’s new pedestrian zone by creating a curated “Granville Street Experience” travel package, partnering with local vendors and promoting it through social media influencers; launch the campaign within 60 days to capture early adopter interest.</t>
+          <t>Introduce a white‑label travel engine for partner agencies, modeled after Priceline’s Partner Network, to enable agencies to brand and sell MONDEE’s inventory while expanding our distribution network.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a beta program to key agency partners within the next 60 days.</t>
+          <t>Launch a dedicated back‑office API for travel advisors, integrating real‑time booking reference tools and workflow automation, and partner with a leading US advisory platform to pilot the solution within the next quarter.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Partner with a leading travel agency network to pilot a white‑label travel engine, leveraging MONDEE’s existing booking platform to capture the market segment targeted by Priceline Partner Network.</t>
+          <t>Develop a white‑label travel engine that allows agencies to brand MONDEE’s booking platform, mirroring Priceline Partner Network’s model, and target mid‑size agencies with a customized onboarding package.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce an automated booking reference management feature that integrates with our API, enabling agencies to streamline operations and compete directly with Expedia TAAP’s new booking reference tools.</t>
+          <t>Introduce a suite of API tools offering real‑time analytics and booking reference management, and offer a 30‑day free trial to agencies that integrate within the next 60 days.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API for travel advisors that offers real‑time inventory, booking reference, and commission tracking, directly addressing the new Expedia TAAP tools and positioning MONDEE as the preferred agency platform.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that includes booking reference management and real‑time inventory, mirroring Expedia TAAP's new tools, to capture the agency segment currently served by competitors.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver’s tourism authority to build a mobile app that highlights Granville Street’s pedestrian zone, offering dynamic routing, event schedules, and local vendor integrations, turning the positive expansion into a new revenue stream.</t>
+          <t>Partner with city tourism boards (e.g., Vancouver) to develop a mobile app that promotes car‑free zones and offers integrated booking for local experiences, leveraging the growing pedestrian‑friendly travel trend highlighted by Downtown Travel.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label integration with Priceline Partner Network to embed MONDEE’s recommendation engine into their platform, ensuring visibility in the same ecosystem that hosts Expedia TAAP and countering the competitive advantage of their white‑label engine.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s platform, and negotiate a revenue‑share model to compete directly with Booking Holdings’ white‑label solution.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors, including real‑time booking reference tools, and initiate a pilot with top agencies to validate integration ease and gather feedback.</t>
+          <t>Develop and release a back‑office API that provides real‑time booking reference tools and automated workflow features for travel agencies, mirroring Expedia TAAP’s new offerings; launch a public developer portal and SDK within 90 days.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Partner with a white‑label travel engine provider or build an in‑house engine to bundle with MONDEE’s platform, positioning it as a turnkey solution for agencies similar to Priceline Partner Network’s offering.</t>
+          <t>Secure a white‑label partnership with a leading travel advisor network to embed MONDEE’s booking engine into their platforms, positioning us as the alternative to Priceline Partner Network; initiate pilot integration within 6 months.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies that use MONDEE’s platform, mirroring Expedia TAAP Rewards, to incentivize higher booking volumes and strengthen loyalty.</t>
+          <t>Introduce an agency‑centric rewards program that offers tiered incentives based on booking volume and API usage, directly competing with Expedia TAAP Rewards; roll out the program to existing partners within 3 months.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API that allows travel advisors to manage bookings, reference numbers, and operational workflows directly within MONDEE, positioning it as a direct alternative to Expedia TAAP’s new tools.</t>
+          <t>Develop and launch a back‑office API for travel advisors that includes real‑time booking reference tools, inventory management, and analytics, positioning MONDEE as a direct competitor to Expedia TAAP’s new suite. Ensure the API is developer‑friendly and offers a quick integration path for agencies.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to launch a mobile‑first itinerary and booking platform for the Granville Street car‑free zone, leveraging MONDEE’s data to capture the surge in local travel demand.</t>
+          <t>Create a mobile application that maps and promotes the new pedestrian‑only Granville Street zone, offering curated itineraries, real‑time event updates, and exclusive local deals to attract both residents and tourists, thereby capitalizing on the city’s expanded downtown travel experience.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine for partner agencies, modeled after Priceline’s Partner Network, to enable agencies to brand and sell MONDEE’s inventory while expanding our distribution network.</t>
+          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to broaden inventory access for agencies, and launch a joint marketing campaign highlighting the expanded product range and seamless agency workflow.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API for travel advisors, integrating real‑time booking reference tools and workflow automation, and partner with a leading US advisory platform to pilot the solution within the next quarter.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new booking reference tools, enabling agencies to manage reservations and reporting directly from MONDEE’s platform.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that allows agencies to brand MONDEE’s booking platform, mirroring Priceline Partner Network’s model, and target mid‑size agencies with a customized onboarding package.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking infrastructure and capture higher margins.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce a suite of API tools offering real‑time analytics and booking reference management, and offer a 30‑day free trial to agencies that integrate within the next 60 days.</t>
+          <t>Partner with a leading travel advisory firm to pilot a co‑branded advisor dashboard that integrates real‑time inventory and pricing, positioning MONDEE as the preferred platform for agency efficiency.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that includes booking reference management and real‑time inventory, mirroring Expedia TAAP's new tools, to capture the agency segment currently served by competitors.</t>
+          <t>Develop a back‑office API and agency tools that mirror Expedia TAAP’s features, enabling travel advisors to manage bookings and inventory directly through MONDEE’s platform, thereby positioning MONDEE as a preferred partner for agencies.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with city tourism boards (e.g., Vancouver) to develop a mobile app that promotes car‑free zones and offers integrated booking for local experiences, leveraging the growing pedestrian‑friendly travel trend highlighted by Downtown Travel.</t>
+          <t>Launch a white‑label travel engine that can be integrated into partner sites, following Priceline Partner Network’s model, to broaden MONDEE’s reach and generate new revenue streams.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s platform, and negotiate a revenue‑share model to compete directly with Booking Holdings’ white‑label solution.</t>
+          <t>Create a Vancouver‑focused travel package that highlights the new pedestrian zone, partnering with local businesses to offer exclusive experiences and promote MONDEE’s platform as the go‑to for city‑centric travel.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API that provides real‑time booking reference tools and automated workflow features for travel agencies, mirroring Expedia TAAP’s new offerings; launch a public developer portal and SDK within 90 days.</t>
+          <t>Launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, and pilot it with a select group of high‑volume agencies to validate integration speed and data accuracy. Offer a free sandbox environment and real‑time support to accelerate adoption.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Secure a white‑label partnership with a leading travel advisor network to embed MONDEE’s booking engine into their platforms, positioning us as the alternative to Priceline Partner Network; initiate pilot integration within 6 months.</t>
+          <t>Build a white‑label travel engine similar to Priceline Partner Network’s platform, enabling partners to embed MONDEE’s booking capabilities under their own brand, and target mid‑market agencies that currently rely on third‑party solutions.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce an agency‑centric rewards program that offers tiered incentives based on booking volume and API usage, directly competing with Expedia TAAP Rewards; roll out the program to existing partners within 3 months.</t>
+          <t>Introduce a tiered rewards program for travel advisors that rewards volume and engagement, integrating it with the new API to provide instant commission boosts and exclusive partner offers, thereby matching Expedia TAAP’s incentive model.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API for travel advisors that includes real‑time booking reference tools, inventory management, and analytics, positioning MONDEE as a direct competitor to Expedia TAAP’s new suite. Ensure the API is developer‑friendly and offers a quick integration path for agencies.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new features, and integrate real‑time data from Vancouver’s car‑free Granville Street to offer advisors instant itinerary optimization.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Create a mobile application that maps and promotes the new pedestrian‑only Granville Street zone, offering curated itineraries, real‑time event updates, and exclusive local deals to attract both residents and tourists, thereby capitalizing on the city’s expanded downtown travel experience.</t>
+          <t>Create a white‑label travel engine for US brands, following Priceline Partner Network’s model, and target agencies that currently rely on Expedia TAAP to secure a share of the advisor market.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Integrate MONDEE’s booking engine with Priceline Partner Network’s white‑label platform to broaden inventory access for agencies, and launch a joint marketing campaign highlighting the expanded product range and seamless agency workflow.</t>
+          <t>Collaborate with Vancouver city officials to curate a travel package centered on the Granville Street pedestrian zone, positioning MONDEE as the preferred platform for urban travel experiences and countering competitors’ focus on back‑office tools.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s new booking reference tools, enabling agencies to manage reservations and reporting directly from MONDEE’s platform.</t>
+          <t>Develop and launch a white‑label travel engine tailored for US travel advisors, mirroring Priceline Partner Network’s model, and position it as a plug‑and‑play solution that integrates with existing advisor workflows.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network, allowing agencies to brand MONDEE’s booking infrastructure and capture higher margins.</t>
+          <t>Introduce a back‑office API suite for travel advisors, enabling real‑time inventory, pricing, and booking management, and promote it through targeted webinars to showcase its efficiency gains over Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Partner with a leading travel advisory firm to pilot a co‑branded advisor dashboard that integrates real‑time inventory and pricing, positioning MONDEE as the preferred platform for agency efficiency.</t>
+          <t>Create a feature set that automates advisor operations—such as dynamic pricing, itinerary optimization, and compliance checks—leveraging AI, and launch a pilot program with a leading US travel advisory firm to demonstrate ROI.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop a back‑office API and agency tools that mirror Expedia TAAP’s features, enabling travel advisors to manage bookings and inventory directly through MONDEE’s platform, thereby positioning MONDEE as a preferred partner for agencies.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time inventory, booking reference, and commission tracking, directly addressing the gap left by Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine that can be integrated into partner sites, following Priceline Partner Network’s model, to broaden MONDEE’s reach and generate new revenue streams.</t>
+          <t>Partner with Vancouver’s tourism authority to build a mobile app that highlights Granville Street’s pedestrian zone events, offering exclusive itineraries and real‑time updates, turning the positive expansion into a revenue stream.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Create a Vancouver‑focused travel package that highlights the new pedestrian zone, partnering with local businesses to offer exclusive experiences and promote MONDEE’s platform as the go‑to for city‑centric travel.</t>
+          <t>Introduce a white‑label travel engine with built‑in sustainability reporting and carbon‑offset options, positioning MONDEE as the eco‑friendly alternative to Priceline Partner Network’s neutral‑sized platform.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors that mirrors Expedia TAAP’s booking reference and workflow tools, and pilot it with a select group of high‑volume agencies to validate integration speed and data accuracy. Offer a free sandbox environment and real‑time support to accelerate adoption.</t>
+          <t>Develop and release a back‑office API suite for travel agencies that includes booking reference tools and real‑time inventory, mirroring Expedia TAAP’s new API and tools, and launch a pilot with 3 key agency partners within 90 days. This will position MONDEE as a preferred tech partner for advisors seeking operational efficiency.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine similar to Priceline Partner Network’s platform, enabling partners to embed MONDEE’s booking capabilities under their own brand, and target mid‑market agencies that currently rely on third‑party solutions.</t>
+          <t>Create a white‑label travel engine similar to Priceline Partner Network, enabling travel agencies to brand MONDEE’s booking platform, and secure at least two agency agreements within 6 months. This will allow agencies to offer a seamless booking experience while driving revenue for MONDEE.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors that rewards volume and engagement, integrating it with the new API to provide instant commission boosts and exclusive partner offers, thereby matching Expedia TAAP’s incentive model.</t>
+          <t>Introduce a rewards program for travel advisors, offering tiered incentives for bookings and API usage, to compete with Expedia TAAP Rewards, and roll it out to existing partners by Q3. This will increase advisor loyalty and encourage higher booking volumes.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new features, and integrate real‑time data from Vancouver’s car‑free Granville Street to offer advisors instant itinerary optimization.</t>
+          <t>Develop a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a pilot with a select group of US travel agencies to secure early adoption and differentiate MONDEE’s platform.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine for US brands, following Priceline Partner Network’s model, and target agencies that currently rely on Expedia TAAP to secure a share of the advisor market.</t>
+          <t>Leverage the Priceline Partner Network’s white‑label engine by integrating MONDEE’s recommendation engine into their platform, offering a co‑branded solution that expands our reach to Booking Holdings’ US brands.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver city officials to curate a travel package centered on the Granville Street pedestrian zone, positioning MONDEE as the preferred platform for urban travel experiences and countering competitors’ focus on back‑office tools.</t>
+          <t>Create a localized experience package for Vancouver’s new pedestrian zone, partnering with local businesses to offer curated tours and promotions, and promote it through MONDEE’s mobile app to capture the growing urban travel market.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop and launch a white‑label travel engine tailored for US travel advisors, mirroring Priceline Partner Network’s model, and position it as a plug‑and‑play solution that integrates with existing advisor workflows.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and pilot it with a select group of US agencies to secure early adoption.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a back‑office API suite for travel advisors, enabling real‑time inventory, pricing, and booking management, and promote it through targeted webinars to showcase its efficiency gains over Expedia TAAP’s new tools.</t>
+          <t>Develop a white‑label travel engine that supports dynamic inventory and pricing, positioning MONDEE as a direct competitor to Priceline Partner Network’s engine, and target mid‑market agencies for rapid deployment.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Create a feature set that automates advisor operations—such as dynamic pricing, itinerary optimization, and compliance checks—leveraging AI, and launch a pilot program with a leading US travel advisory firm to demonstrate ROI.</t>
+          <t>Create a US‑focused advisory platform that integrates real‑time booking, analytics, and back‑office workflows, and launch a co‑marketing campaign with key travel advisors to showcase MONDEE’s end‑to‑end solution.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time inventory, booking reference, and commission tracking, directly addressing the gap left by Expedia TAAP’s new tools.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors that integrates with MONDEE’s existing platform, mirroring Expedia TAAP’s new tools, to capture the agency segment and provide real‑time booking reference management. Prioritize API security and partner with key agencies to pilot the solution within the next 90 days.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to build a mobile app that highlights Granville Street’s pedestrian zone events, offering exclusive itineraries and real‑time updates, turning the positive expansion into a revenue stream.</t>
+          <t>Leverage the Priceline Partner Network’s white‑label engine by creating a co‑branded travel engine that offers unique local experiences, positioning MONDEE as a niche provider for boutique travel packages. Secure a pilot partnership with a mid‑size agency in Q3 to validate demand and refine the white‑label offering.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine with built‑in sustainability reporting and carbon‑offset options, positioning MONDEE as the eco‑friendly alternative to Priceline Partner Network’s neutral‑sized platform.</t>
+          <t>Capitalize on Vancouver’s car‑free Granville Street expansion by launching a localized mobile guide and booking widget that promotes pedestrian‑friendly itineraries, positioning MONDEE as the go‑to platform for sustainable urban travel. Collaborate with local tourism boards to feature the widget in their marketing campaigns starting next month.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel agencies that includes booking reference tools and real‑time inventory, mirroring Expedia TAAP’s new API and tools, and launch a pilot with 3 key agency partners within 90 days. This will position MONDEE as a preferred tech partner for advisors seeking operational efficiency.</t>
+          <t>Launch a dedicated back‑office API and developer portal for travel advisors, mirroring Expedia TAAP’s new tools, and provide comprehensive SDKs and real‑time support to accelerate integration.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine similar to Priceline Partner Network, enabling travel agencies to brand MONDEE’s booking platform, and secure at least two agency agreements within 6 months. This will allow agencies to offer a seamless booking experience while driving revenue for MONDEE.</t>
+          <t>Introduce a tiered rewards program for agencies that book through MONDEE, offering points, discounts, and exclusive partner perks to emulate Expedia TAAP Rewards and boost loyalty.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a rewards program for travel advisors, offering tiered incentives for bookings and API usage, to compete with Expedia TAAP Rewards, and roll it out to existing partners by Q3. This will increase advisor loyalty and encourage higher booking volumes.</t>
+          <t>Develop or acquire a white‑label travel engine that agencies can brand and embed, positioning MONDEE as a direct competitor to Priceline Partner Network’s quiet engine and expanding our agency‑centric product suite.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and launch a pilot with a select group of US travel agencies to secure early adoption and differentiate MONDEE’s platform.</t>
+          <t>Develop and release a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, to attract agencies seeking integrated booking solutions.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Leverage the Priceline Partner Network’s white‑label engine by integrating MONDEE’s recommendation engine into their platform, offering a co‑branded solution that expands our reach to Booking Holdings’ US brands.</t>
+          <t>Collaborate with Vancouver’s tourism board to embed Granville Street pedestrian‑zone itineraries into MONDEE’s app, positioning us as the go‑to platform for urban travel experiences.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a localized experience package for Vancouver’s new pedestrian zone, partnering with local businesses to offer curated tours and promotions, and promote it through MONDEE’s mobile app to capture the growing urban travel market.</t>
+          <t>Create a white‑label travel engine for US brands, enabling them to embed MONDEE’s booking technology and compete with Priceline Partner Network’s quiet expansion.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and pilot it with a select group of US agencies to secure early adoption.</t>
+          <t>Develop a US‑focused travel advisor portal that mirrors Expedia TAAP’s behind‑the‑scenes engine, integrating real‑time inventory, booking, and analytics to attract advisors seeking a unified platform.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that supports dynamic inventory and pricing, positioning MONDEE as a direct competitor to Priceline Partner Network’s engine, and target mid‑market agencies for rapid deployment.</t>
+          <t>Launch a back‑office API suite for partners, enabling them to automate inventory management, pricing, and reporting, directly addressing the new tools Expedia has introduced.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Create a US‑focused advisory platform that integrates real‑time booking, analytics, and back‑office workflows, and launch a co‑marketing campaign with key travel advisors to showcase MONDEE’s end‑to‑end solution.</t>
+          <t>Create a white‑label travel engine for resellers, positioning MONDEE as a flexible alternative to Priceline’s quiet engine, and include a revenue‑sharing model to incentivize adoption.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors that integrates with MONDEE’s existing platform, mirroring Expedia TAAP’s new tools, to capture the agency segment and provide real‑time booking reference management. Prioritize API security and partner with key agencies to pilot the solution within the next 90 days.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that extends beyond booking, offering real‑time inventory, dynamic pricing, and automated commission calculations, directly addressing Expedia TAAP’s new tools and positioning MONDEE as the preferred partner for agencies.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leverage the Priceline Partner Network’s white‑label engine by creating a co‑branded travel engine that offers unique local experiences, positioning MONDEE as a niche provider for boutique travel packages. Secure a pilot partnership with a mid‑size agency in Q3 to validate demand and refine the white‑label offering.</t>
+          <t>Collaborate with Vancouver’s tourism authority to develop a mobile‑first itinerary builder for the new car‑free Granville Street zone, integrating real‑time event data and local vendor partnerships, thereby capitalizing on the city’s pedestrian expansion and differentiating MONDEE’s experiential content.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Capitalize on Vancouver’s car‑free Granville Street expansion by launching a localized mobile guide and booking widget that promotes pedestrian‑friendly itineraries, positioning MONDEE as the go‑to platform for sustainable urban travel. Collaborate with local tourism boards to feature the widget in their marketing campaigns starting next month.</t>
+          <t>Introduce a white‑label travel engine tailored for boutique agencies, leveraging MONDEE’s existing booking infrastructure, to compete with Priceline Partner Network’s quiet white‑label offering and capture market share among agencies seeking customizable solutions.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API and developer portal for travel advisors, mirroring Expedia TAAP’s new tools, and provide comprehensive SDKs and real‑time support to accelerate integration.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, to enable seamless booking reference management and real‑time inventory access for advisors.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies that book through MONDEE, offering points, discounts, and exclusive partner perks to emulate Expedia TAAP Rewards and boost loyalty.</t>
+          <t>Introduce a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, to incentivize higher booking volumes and strengthen loyalty among agency partners.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Develop or acquire a white‑label travel engine that agencies can brand and embed, positioning MONDEE as a direct competitor to Priceline Partner Network’s quiet engine and expanding our agency‑centric product suite.</t>
+          <t>Partner with a white‑label travel engine provider, such as Priceline Partner Network, to embed a customizable booking platform within MONDEE’s advisor portal, offering agencies a scalable, cost‑effective solution while expanding our market reach.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, to attract agencies seeking integrated booking solutions.</t>
+          <t>Develop and beta‑test a back‑office API and tools for travel advisors, mirroring Expedia TAAP’s new offering, to retain advisor loyalty and capture the emerging market segment.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver’s tourism board to embed Granville Street pedestrian‑zone itineraries into MONDEE’s app, positioning us as the go‑to platform for urban travel experiences.</t>
+          <t>Launch a white‑label travel engine tailored for US brands, positioning MONDEE as a direct competitor to Priceline Partner Network’s white‑label solution and targeting mid‑size agencies seeking customizable platforms.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine for US brands, enabling them to embed MONDEE’s booking technology and compete with Priceline Partner Network’s quiet expansion.</t>
+          <t>Partner with Vancouver’s tourism board to build a mobile app that offers real‑time navigation, event listings, and booking integration for the new pedestrian zone, leveraging the increased foot traffic to showcase MONDEE’s platform to local travelers.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a US‑focused travel advisor portal that mirrors Expedia TAAP’s behind‑the‑scenes engine, integrating real‑time inventory, booking, and analytics to attract advisors seeking a unified platform.</t>
+          <t>Accelerate the rollout of MONDEE’s own back‑office API, adding real‑time inventory, booking, and cancellation capabilities to give US travel advisors a direct alternative to Expedia TAAP’s new tools.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for partners, enabling them to automate inventory management, pricing, and reporting, directly addressing the new tools Expedia has introduced.</t>
+          <t>Launch a white‑label partnership program targeting US travel agencies, offering MONDEE’s engine with customizable branding and integration support to compete with Priceline Partner Network’s quiet engine.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine for resellers, positioning MONDEE as a flexible alternative to Priceline’s quiet engine, and include a revenue‑sharing model to incentivize adoption.</t>
+          <t>Introduce a bundled post‑booking service that pairs travel advisory tools with itinerary management and dynamic pricing alerts, positioning MONDEE as a comprehensive solution beyond simple bookings, directly countering Expedia TAAP’s expansion.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that extends beyond booking, offering real‑time inventory, dynamic pricing, and automated commission calculations, directly addressing Expedia TAAP’s new tools and positioning MONDEE as the preferred partner for agencies.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, focusing on real‑time booking reference and workflow automation, and promote it through a targeted webinar series for agencies.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver’s tourism authority to develop a mobile‑first itinerary builder for the new car‑free Granville Street zone, integrating real‑time event data and local vendor partnerships, thereby capitalizing on the city’s pedestrian expansion and differentiating MONDEE’s experiential content.</t>
+          <t>Partner with Vancouver’s city council to integrate MONDEE’s booking platform into the Granville Street pedestrian zone promotion, offering exclusive travel packages and real‑time visitor data analytics to enhance the downtown experience.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine tailored for boutique agencies, leveraging MONDEE’s existing booking infrastructure, to compete with Priceline Partner Network’s quiet white‑label offering and capture market share among agencies seeking customizable solutions.</t>
+          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling third‑party brands to embed MONDEE’s inventory and booking capabilities, and launch a pilot with a mid‑market OTA to capture new revenue streams.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel agencies, mirroring Expedia TAAP’s new tools, to enable seamless booking reference management and real‑time inventory access for advisors.</t>
+          <t>Develop and launch a back‑office API suite for travel agencies that mirrors Expedia TAAP’s new booking reference and tools, enabling agencies to manage inventory, pricing, and commissions directly from MONDEE’s platform; pilot with a select group of top advisors within 90 days.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, to incentivize higher booking volumes and strengthen loyalty among agency partners.</t>
+          <t>Partner with a leading white‑label travel engine (e.g., Priceline Partner Network) to embed a customizable booking engine into MONDEE’s advisor portal, offering agencies a seamless, branded experience and expanding MONDEE’s reach into the B2B market within 6 months.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partner with a white‑label travel engine provider, such as Priceline Partner Network, to embed a customizable booking platform within MONDEE’s advisor portal, offering agencies a scalable, cost‑effective solution while expanding our market reach.</t>
+          <t>Introduce a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, that incentivizes higher booking volumes and platform usage; roll out the program with a marketing campaign targeting existing advisor clients over the next quarter.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and beta‑test a back‑office API and tools for travel advisors, mirroring Expedia TAAP’s new offering, to retain advisor loyalty and capture the emerging market segment.</t>
+          <t>Launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and promote it through a targeted advisor‑centric marketing campaign to capture the growing demand for behind‑the‑scenes booking solutions.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine tailored for US brands, positioning MONDEE as a direct competitor to Priceline Partner Network’s white‑label solution and targeting mid‑size agencies seeking customizable platforms.</t>
+          <t>Partner with Vancouver’s tourism authority to develop a mobile guide and booking integration for the new car‑free Granville Street zone, positioning MONDEE as the go‑to platform for urban travel experiences.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism board to build a mobile app that offers real‑time navigation, event listings, and booking integration for the new pedestrian zone, leveraging the increased foot traffic to showcase MONDEE’s platform to local travelers.</t>
+          <t>Introduce a white‑label travel engine tailored for US brands, leveraging lessons from Priceline Partner Network, and secure pilot agreements with mid‑market travel agencies to quickly scale adoption.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accelerate the rollout of MONDEE’s own back‑office API, adding real‑time inventory, booking, and cancellation capabilities to give US travel advisors a direct alternative to Expedia TAAP’s new tools.</t>
+          <t>Develop a dedicated travel‑advisor platform that mirrors Expedia TAAP’s behind‑the‑scenes engine, integrating real‑time inventory and booking tools, and launch a pilot with 5 key US advisors within 90 days. Offer a revenue‑share model to incentivize adoption and collect feedback for iterative improvement.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launch a white‑label partnership program targeting US travel agencies, offering MONDEE’s engine with customizable branding and integration support to compete with Priceline Partner Network’s quiet engine.</t>
+          <t>Release a comprehensive back‑office API suite similar to Expedia’s new tools, enabling partners to automate inventory management, pricing, and reporting, and publish SDKs in the next product sprint. Schedule a webinar for partners to demonstrate integration benefits and gather beta usage data.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce a bundled post‑booking service that pairs travel advisory tools with itinerary management and dynamic pricing alerts, positioning MONDEE as a comprehensive solution beyond simple bookings, directly countering Expedia TAAP’s expansion.</t>
+          <t>Introduce a white‑label travel engine akin to Priceline Partner Network, allowing agencies to brand the booking experience while leveraging MONDEE’s core technology, and target 10 agencies in the first quarter. Provide a 30‑day free trial and dedicated support to accelerate onboarding.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that mirrors Expedia TAAP’s new tools, focusing on real‑time booking reference and workflow automation, and promote it through a targeted webinar series for agencies.</t>
+          <t>Launch a back‑office API for travel advisors that offers real‑time inventory sync, AI‑driven pricing, and booking reference tools, directly addressing the features Expedia TAAP has introduced. This will position MONDEE as a competitive alternative for agencies seeking streamlined operations.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s city council to integrate MONDEE’s booking platform into the Granville Street pedestrian zone promotion, offering exclusive travel packages and real‑time visitor data analytics to enhance the downtown experience.</t>
+          <t>Collaborate with Vancouver's tourism authority to develop a digital guide and booking widget for the new car‑free Granville Street zone, capitalizing on the positive market sentiment. Embed this guide into MONDEE’s platform to attract travelers looking for unique downtown experiences.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine similar to Priceline Partner Network, enabling third‑party brands to embed MONDEE’s inventory and booking capabilities, and launch a pilot with a mid‑market OTA to capture new revenue streams.</t>
+          <t>Acquire or license a white‑label travel engine similar to Priceline Partner Network to provide agencies with a scalable, branded booking solution, countering Booking Holdings’ backend advantage. Integrate the engine into MONDEE’s existing API suite to offer seamless agency onboarding and revenue sharing.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel agencies that mirrors Expedia TAAP’s new booking reference and tools, enabling agencies to manage inventory, pricing, and commissions directly from MONDEE’s platform; pilot with a select group of top advisors within 90 days.</t>
+          <t>Initiate a rapid development sprint to build a back‑office API and agency‑tool suite that mirrors Expedia TAAP’s new offerings, and launch a beta to our top 15 agency partners within 90 days. This will enable agencies to manage bookings, references, and reporting directly through MONDEE, positioning us as a direct competitor to TAAP.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Partner with a leading white‑label travel engine (e.g., Priceline Partner Network) to embed a customizable booking engine into MONDEE’s advisor portal, offering agencies a seamless, branded experience and expanding MONDEE’s reach into the B2B market within 6 months.</t>
+          <t>Introduce a tiered rewards program for agencies using MONDEE, offering commission boosts, exclusive content, and early access to new features, mirroring Expedia TAAP Rewards, and pilot it with our top 10 agencies over the next 60 days. Track engagement and adjust reward thresholds quarterly to maximize agency retention.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors, similar to Expedia TAAP Rewards, that incentivizes higher booking volumes and platform usage; roll out the program with a marketing campaign targeting existing advisor clients over the next quarter.</t>
+          <t>Secure a partnership with a leading white‑label travel engine provider or develop an in‑house engine to offer agencies a seamless booking solution, directly countering Priceline Partner Network’s quiet power, and roll it out to 20 agencies within 120 days. Provide API access and integration support to ensure rapid adoption and differentiation from competitors.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and promote it through a targeted advisor‑centric marketing campaign to capture the growing demand for behind‑the‑scenes booking solutions.</t>
+          <t>Market conditions are currently stable.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to develop a mobile guide and booking integration for the new car‑free Granville Street zone, positioning MONDEE as the go‑to platform for urban travel experiences.</t>
+          <t>No high-priority competitor moves detected in this timeframe.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine tailored for US brands, leveraging lessons from Priceline Partner Network, and secure pilot agreements with mid‑market travel agencies to quickly scale adoption.</t>
+          <t>Continue tracking standard sector intelligence.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a dedicated travel‑advisor platform that mirrors Expedia TAAP’s behind‑the‑scenes engine, integrating real‑time inventory and booking tools, and launch a pilot with 5 key US advisors within 90 days. Offer a revenue‑share model to incentivize adoption and collect feedback for iterative improvement.</t>
+          <t>Develop a back‑office API and toolset for travel advisors, mirroring Expedia TAAP’s new offerings, and launch a pilot with a select group of US agencies to secure early adoption.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Release a comprehensive back‑office API suite similar to Expedia’s new tools, enabling partners to automate inventory management, pricing, and reporting, and publish SDKs in the next product sprint. Schedule a webinar for partners to demonstrate integration benefits and gather beta usage data.</t>
+          <t>Create a white‑label travel engine similar to Priceline Partner Network’s platform, enabling partners to embed MONDEE’s booking capabilities and generate new distribution revenue.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine akin to Priceline Partner Network, allowing agencies to brand the booking experience while leveraging MONDEE’s core technology, and target 10 agencies in the first quarter. Provide a 30‑day free trial and dedicated support to accelerate onboarding.</t>
+          <t>Introduce a real‑time analytics dashboard for travel advisors that aggregates inventory and pricing data, positioning MONDEE as a strategic partner beyond simple booking services.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API for travel advisors that offers real‑time inventory sync, AI‑driven pricing, and booking reference tools, directly addressing the features Expedia TAAP has introduced. This will position MONDEE as a competitive alternative for agencies seeking streamlined operations.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors that integrates real‑time inventory, booking reference, and commission management, mirroring Expedia TAAP’s new tools, and beta‑test it with a select group of top agencies to secure early adoption. Offer a free pilot period and gather feedback to iterate quickly, positioning MONDEE as the most advisor‑friendly platform in the market.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Collaborate with Vancouver's tourism authority to develop a digital guide and booking widget for the new car‑free Granville Street zone, capitalizing on the positive market sentiment. Embed this guide into MONDEE’s platform to attract travelers looking for unique downtown experiences.</t>
+          <t>Leverage the growing trend of pedestrian‑friendly downtowns by partnering with city planners in Vancouver to create a dedicated API that aggregates real‑time pedestrian zone data, enabling travel advisors to recommend optimized itineraries and exclusive experiences. Promote this feature through targeted marketing to agencies focusing on experiential travel.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acquire or license a white‑label travel engine similar to Priceline Partner Network to provide agencies with a scalable, branded booking solution, countering Booking Holdings’ backend advantage. Integrate the engine into MONDEE’s existing API suite to offer seamless agency onboarding and revenue sharing.</t>
+          <t>Launch a white‑label travel engine similar to Priceline Partner Network, allowing partner agencies to brand the platform while accessing MONDEE’s inventory and pricing, and target mid‑market agencies that currently rely on Expedia TAAP for back‑office solutions. Offer a revenue‑share model to incentivize rapid adoption and expand our market footprint.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Initiate a rapid development sprint to build a back‑office API and agency‑tool suite that mirrors Expedia TAAP’s new offerings, and launch a beta to our top 15 agency partners within 90 days. This will enable agencies to manage bookings, references, and reporting directly through MONDEE, positioning us as a direct competitor to TAAP.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with our existing platform to streamline agency operations and reduce friction in booking management. Prioritize API documentation and a sandbox environment to accelerate partner adoption within the next quarter.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies using MONDEE, offering commission boosts, exclusive content, and early access to new features, mirroring Expedia TAAP Rewards, and pilot it with our top 10 agencies over the next 60 days. Track engagement and adjust reward thresholds quarterly to maximize agency retention.</t>
+          <t>Introduce a tiered rewards program for travel agencies using MONDEE, similar to Expedia TAAP Rewards, to incentivize higher booking volumes and foster loyalty. Pilot the program with key agency partners and measure lift in bookings over a 90‑day period.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Secure a partnership with a leading white‑label travel engine provider or develop an in‑house engine to offer agencies a seamless booking solution, directly countering Priceline Partner Network’s quiet power, and roll it out to 20 agencies within 120 days. Provide API access and integration support to ensure rapid adoption and differentiation from competitors.</t>
+          <t>Leverage our white‑label engine capabilities to offer a customizable travel booking platform to mid‑market agencies, positioning MONDEE as a flexible alternative to Priceline Partner Network. Deploy a targeted outreach campaign to agencies currently using PPN, highlighting integration ease and cost advantages.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Market conditions are currently stable.</t>
+          <t>Develop a modular, behind‑the‑scenes API platform for US travel advisors to match Expedia TAAP, and pilot it with three key agencies to secure early adoption.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No high-priority competitor moves detected in this timeframe.</t>
+          <t>Initiate a partnership with Booking Holdings to embed MONDEE’s white‑label travel engine into the Priceline Partner Network, positioning it as a differentiated solution for US brands.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Continue tracking standard sector intelligence.</t>
+          <t>Launch a Vancouver‑focused travel bundle that highlights the new pedestrian‑only Granville Street zone, partnering with local businesses to offer exclusive discounts and promote the experience through targeted social media campaigns.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a back‑office API and toolset for travel advisors, mirroring Expedia TAAP’s new offerings, and launch a pilot with a select group of US agencies to secure early adoption.</t>
+          <t>Launch a dedicated back‑office API for US travel advisors that mirrors Expedia TAAP’s functionality, enabling our partners to access real‑time inventory and booking tools; pilot it with a select group of advisors within the next 90 days. This will position MONDEE as the preferred tech partner for advisors seeking seamless integration.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine similar to Priceline Partner Network’s platform, enabling partners to embed MONDEE’s booking capabilities and generate new distribution revenue.</t>
+          <t>Develop a plug‑in that extends our existing platform to consume Expedia TAAP’s new back‑office API, allowing our clients to leverage their enhanced tools without leaving MONDEE; begin integration testing by the end of Q3.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce a real‑time analytics dashboard for travel advisors that aggregates inventory and pricing data, positioning MONDEE as a strategic partner beyond simple booking services.</t>
+          <t>Introduce a white‑label travel engine similar to Priceline Partner Network’s offering, targeting boutique agencies that require customizable booking solutions; launch a beta program with 5 agencies within 60 days.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors that integrates real‑time inventory, booking reference, and commission management, mirroring Expedia TAAP’s new tools, and beta‑test it with a select group of top agencies to secure early adoption. Offer a free pilot period and gather feedback to iterate quickly, positioning MONDEE as the most advisor‑friendly platform in the market.</t>
+          <t>Initiate a rapid development sprint to build a back‑office API and booking‑reference toolkit for travel advisors, mirroring Expedia TAAP’s new offering. Pilot it with 3 key agency partners within 90 days.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leverage the growing trend of pedestrian‑friendly downtowns by partnering with city planners in Vancouver to create a dedicated API that aggregates real‑time pedestrian zone data, enabling travel advisors to recommend optimized itineraries and exclusive experiences. Promote this feature through targeted marketing to agencies focusing on experiential travel.</t>
+          <t>Leverage the Vancouver pedestrian‑zone expansion by launching a localized travel package app that bundles walking tours, local events, and real‑time navigation, and partner with Downtown Travel to promote it to tourists.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine similar to Priceline Partner Network, allowing partner agencies to brand the platform while accessing MONDEE’s inventory and pricing, and target mid‑market agencies that currently rely on Expedia TAAP for back‑office solutions. Offer a revenue‑share model to incentivize rapid adoption and expand our market footprint.</t>
+          <t>Develop a white‑label travel engine inspired by Priceline Partner Network’s model, focusing on niche markets (e.g., eco‑tourism), and offer it to mid‑size agencies as a plug‑and‑play solution within 6 months.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and integrate it with our existing platform to streamline agency operations and reduce friction in booking management. Prioritize API documentation and a sandbox environment to accelerate partner adoption within the next quarter.</t>
+          <t>Develop and launch a white‑label back‑office API and booking reference tools for travel agencies, mirroring Expedia TAAP’s recent rollout, and immediately market it to the same advisor segments that have adopted TAAP. Include a rapid onboarding kit and API documentation to reduce integration time.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel agencies using MONDEE, similar to Expedia TAAP Rewards, to incentivize higher booking volumes and foster loyalty. Pilot the program with key agency partners and measure lift in bookings over a 90‑day period.</t>
+          <t>Introduce a tiered rewards program for travel advisors using MONDEE’s platform, similar to Expedia TAAP Rewards, to increase platform stickiness and incentivize higher booking volumes.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leverage our white‑label engine capabilities to offer a customizable travel booking platform to mid‑market agencies, positioning MONDEE as a flexible alternative to Priceline Partner Network. Deploy a targeted outreach campaign to agencies currently using PPN, highlighting integration ease and cost advantages.</t>
+          <t>Partner with a leading travel advisor network to pilot a joint analytics dashboard that aggregates inventory and performance metrics, positioning MONDEE as a data‑driven alternative to the white‑label engine of Priceline Partner Network.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a modular, behind‑the‑scenes API platform for US travel advisors to match Expedia TAAP, and pilot it with three key agencies to secure early adoption.</t>
+          <t>Develop and launch a dedicated travel‑advisor platform that mirrors Expedia TAAP, offering a back‑office API and real‑time booking tools for US travel agencies, and promote it through targeted outreach to agencies in key markets. This will position MONDEE as the preferred B2B partner for advisors seeking seamless integration and higher commission rates.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Initiate a partnership with Booking Holdings to embed MONDEE’s white‑label travel engine into the Priceline Partner Network, positioning it as a differentiated solution for US brands.</t>
+          <t>Introduce a white‑label travel engine for US brands, allowing them to rebrand MONDEE’s booking platform and integrate it into their own sites, and market this offering to mid‑size travel retailers and airlines. This will counter Priceline’s push and capture a new revenue stream from brands seeking cost‑effective tech solutions.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Launch a Vancouver‑focused travel bundle that highlights the new pedestrian‑only Granville Street zone, partnering with local businesses to offer exclusive discounts and promote the experience through targeted social media campaigns.</t>
+          <t>Create a curated walking‑tour experience for Vancouver’s new car‑free Granville Street, partnering with local cafés, galleries, and tour guides to offer exclusive itineraries through the MONDEE app. Promote this experience to eco‑conscious travelers and leverage the city’s increased foot traffic to boost bookings.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API for US travel advisors that mirrors Expedia TAAP’s functionality, enabling our partners to access real‑time inventory and booking tools; pilot it with a select group of advisors within the next 90 days. This will position MONDEE as the preferred tech partner for advisors seeking seamless integration.</t>
+          <t>Launch a US-focused travel advisor platform that mirrors Expedia TAAP, integrating a back‑office API to streamline operations and position it as a more flexible, data‑driven alternative.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a plug‑in that extends our existing platform to consume Expedia TAAP’s new back‑office API, allowing our clients to leverage their enhanced tools without leaving MONDEE; begin integration testing by the end of Q3.</t>
+          <t>Develop a white‑label travel engine leveraging MONDEE’s existing technology, targeting partners who currently rely on Priceline Partner Network, and offer a revenue‑sharing model to attract them.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine similar to Priceline Partner Network’s offering, targeting boutique agencies that require customizable booking solutions; launch a beta program with 5 agencies within 60 days.</t>
+          <t>Introduce an AI‑powered recommendation layer within our platform that provides real‑time pricing and inventory insights to travel advisors, differentiating from Expedia’s neutral API offerings.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Initiate a rapid development sprint to build a back‑office API and booking‑reference toolkit for travel advisors, mirroring Expedia TAAP’s new offering. Pilot it with 3 key agency partners within 90 days.</t>
+          <t>Launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, to capture agency traffic and provide real‑time booking reference capabilities, positioning MONDEE as the go‑to partner for agencies seeking integrated solutions.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leverage the Vancouver pedestrian‑zone expansion by launching a localized travel package app that bundles walking tours, local events, and real‑time navigation, and partner with Downtown Travel to promote it to tourists.</t>
+          <t>Secure a white‑label partnership with a major travel platform such as Priceline Partner Network to embed MONDEE’s engine, expanding distribution reach while leveraging existing customer bases.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine inspired by Priceline Partner Network’s model, focusing on niche markets (e.g., eco‑tourism), and offer it to mid‑size agencies as a plug‑and‑play solution within 6 months.</t>
+          <t>Create a localized travel package for Vancouver’s new car‑free Granville Street zone, offering curated walking tours and partner discounts, and promote it through social media and travel advisor networks to capture early adopters.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a white‑label back‑office API and booking reference tools for travel agencies, mirroring Expedia TAAP’s recent rollout, and immediately market it to the same advisor segments that have adopted TAAP. Include a rapid onboarding kit and API documentation to reduce integration time.</t>
+          <t>Develop and release a back‑office API suite for travel advisors, including booking reference and workflow automation tools, and launch a dedicated developer portal with SDKs and real‑time support to match Expedia TAAP’s recent feature set.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors using MONDEE’s platform, similar to Expedia TAAP Rewards, to increase platform stickiness and incentivize higher booking volumes.</t>
+          <t>Create a white‑label travel engine partnership program that allows agencies to embed MONDEE’s booking engine into their own sites, offering revenue‑sharing and co‑branding options to compete with Priceline Partner Network’s model.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partner with a leading travel advisor network to pilot a joint analytics dashboard that aggregates inventory and performance metrics, positioning MONDEE as a data‑driven alternative to the white‑label engine of Priceline Partner Network.</t>
+          <t>Pilot a rewards program for travel advisors that offers tiered incentives based on booking volume and engagement, and integrate it into the advisor dashboard to drive adoption and loyalty, mirroring Expedia TAAP Rewards.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated travel‑advisor platform that mirrors Expedia TAAP, offering a back‑office API and real‑time booking tools for US travel agencies, and promote it through targeted outreach to agencies in key markets. This will position MONDEE as the preferred B2B partner for advisors seeking seamless integration and higher commission rates.</t>
+          <t>Develop a dedicated back‑office API and advisor‑tool suite that mirrors Expedia TAAP, enabling travel agencies to embed MONDEE’s itinerary planning and booking engine directly into their workflows, and launch a pilot with 3 key US advisors within 90 days.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine for US brands, allowing them to rebrand MONDEE’s booking platform and integrate it into their own sites, and market this offering to mid‑size travel retailers and airlines. This will counter Priceline’s push and capture a new revenue stream from brands seeking cost‑effective tech solutions.</t>
+          <t>Partner with Vancouver’s city council and local businesses to create a branded mobile guide and booking widget for the new Car‑Free Granville Street zone, positioning MONDEE as the go‑to platform for visitors seeking curated downtown experiences, and roll it out during the summer peak.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a curated walking‑tour experience for Vancouver’s new car‑free Granville Street, partnering with local cafés, galleries, and tour guides to offer exclusive itineraries through the MONDEE app. Promote this experience to eco‑conscious travelers and leverage the city’s increased foot traffic to boost bookings.</t>
+          <t>Introduce a white‑label travel engine tailored for US brands, leveraging MONDEE’s existing API, and secure at least two partner agreements with regional travel agencies or hospitality chains within the next 6 months to counter Priceline’s push.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a US-focused travel advisor platform that mirrors Expedia TAAP, integrating a back‑office API to streamline operations and position it as a more flexible, data‑driven alternative.</t>
+          <t>Develop a US‑focused behind‑the‑scenes engine for travel advisors that incorporates AI‑driven itinerary optimization and a unified dashboard, and launch a pilot with 10 top agencies to secure early adoption before Expedia’s TAAP gains full market penetration.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine leveraging MONDEE’s existing technology, targeting partners who currently rely on Priceline Partner Network, and offer a revenue‑sharing model to attract them.</t>
+          <t>Release a comprehensive back‑office API bundle that offers real‑time inventory, dynamic pricing, and automated compliance checks, and promote it as a plug‑and‑play alternative to Expedia’s new tools through targeted webinars for agencies.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Introduce an AI‑powered recommendation layer within our platform that provides real‑time pricing and inventory insights to travel advisors, differentiating from Expedia’s neutral API offerings.</t>
+          <t>Secure a partnership with a leading travel agency network to deploy MONDEE’s white‑label engine, emphasizing its seamless integration and data‑ownership benefits, thereby positioning us as a direct competitor to Priceline Partner Network’s quiet expansion.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, to capture agency traffic and provide real‑time booking reference capabilities, positioning MONDEE as the go‑to partner for agencies seeking integrated solutions.</t>
+          <t>Develop and launch a back‑office API suite for travel advisors that includes booking reference tools and real‑time inventory, and run a targeted outreach campaign to agencies currently using Expedia TAAP to showcase MONDEE’s superior integration and cost‑efficiency.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Secure a white‑label partnership with a major travel platform such as Priceline Partner Network to embed MONDEE’s engine, expanding distribution reach while leveraging existing customer bases.</t>
+          <t>Create a curated 'Granville Street Experience' package that bundles local attractions, dining, and walking tours, and partner with Vancouver businesses to offer exclusive discounts, leveraging the new pedestrian zone to drive bookings through MONDEE’s platform.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Create a localized travel package for Vancouver’s new car‑free Granville Street zone, offering curated walking tours and partner discounts, and promote it through social media and travel advisor networks to capture early adopters.</t>
+          <t>Build a white‑label travel engine that can be embedded in partner agencies’ websites, and position it as a cost‑effective alternative to Priceline Partner Network’s engine, targeting agencies that rely on white‑label solutions for their clients.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API suite for travel advisors, including booking reference and workflow automation tools, and launch a dedicated developer portal with SDKs and real‑time support to match Expedia TAAP’s recent feature set.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a sandbox for agencies to integrate with MONDEE’s booking engine within 90 days. Include real‑time inventory, booking reference generation, and automated commission calculations to streamline agency operations.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Create a white‑label travel engine partnership program that allows agencies to embed MONDEE’s booking engine into their own sites, offering revenue‑sharing and co‑branding options to compete with Priceline Partner Network’s model.</t>
+          <t>Introduce a tiered rewards program for travel advisors similar to Expedia TAAP Rewards, with instant points for each booking and quarterly bonus tiers, to incentivize partner loyalty and increase booking volume. Launch the program within 60 days and promote it through targeted webinars and agency newsletters.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pilot a rewards program for travel advisors that offers tiered incentives based on booking volume and engagement, and integrate it into the advisor dashboard to drive adoption and loyalty, mirroring Expedia TAAP Rewards.</t>
+          <t>Develop a white‑label travel engine platform, inspired by Priceline Partner Network, that allows agencies to brand MONDEE’s booking interface and integrate it into their own sites, launching a pilot with 5 key agencies in 120 days. Provide API access and dedicated support to ensure seamless deployment and gather feedback for iterative improvement.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a dedicated back‑office API and advisor‑tool suite that mirrors Expedia TAAP, enabling travel agencies to embed MONDEE’s itinerary planning and booking engine directly into their workflows, and launch a pilot with 3 key US advisors within 90 days.</t>
+          <t>Develop a dedicated API integration layer that allows travel advisors to pull MONDEE’s itinerary optimization data directly into Expedia TAAP, positioning MONDEE as the preferred data partner for US travel advisors.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s city council and local businesses to create a branded mobile guide and booking widget for the new Car‑Free Granville Street zone, positioning MONDEE as the go‑to platform for visitors seeking curated downtown experiences, and roll it out during the summer peak.</t>
+          <t>Launch a white‑label travel engine tailored for US brands, mirroring Priceline Partner Network’s model, and target mid‑market travel agencies seeking a customizable booking platform.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine tailored for US brands, leveraging MONDEE’s existing API, and secure at least two partner agreements with regional travel agencies or hospitality chains within the next 6 months to counter Priceline’s push.</t>
+          <t>Partner with Vancouver’s tourism authority to create a pedestrian‑centric mobile guide app that highlights the new car‑free Granville Street, positioning MONDEE as the go‑to tech partner for sustainable urban travel experiences.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a US‑focused behind‑the‑scenes engine for travel advisors that incorporates AI‑driven itinerary optimization and a unified dashboard, and launch a pilot with 10 top agencies to secure early adoption before Expedia’s TAAP gains full market penetration.</t>
+          <t>Launch a US‑focused travel advisor platform that mirrors Expedia TAAP, integrating a robust back‑office API and real‑time inventory tools to give advisors seamless booking and reporting capabilities.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Release a comprehensive back‑office API bundle that offers real‑time inventory, dynamic pricing, and automated compliance checks, and promote it as a plug‑and‑play alternative to Expedia’s new tools through targeted webinars for agencies.</t>
+          <t>Introduce a white‑label travel engine partnership program similar to Priceline Partner Network, allowing agencies to brand our booking engine while we handle inventory, pricing, and compliance.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Secure a partnership with a leading travel agency network to deploy MONDEE’s white‑label engine, emphasizing its seamless integration and data‑ownership benefits, thereby positioning us as a direct competitor to Priceline Partner Network’s quiet expansion.</t>
+          <t>Deploy advanced data‑driven analytics dashboards for advisors, offering predictive pricing, demand forecasting, and personalized travel recommendations that differentiate us from generic competitor APIs.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and launch a back‑office API suite for travel advisors that includes booking reference tools and real‑time inventory, and run a targeted outreach campaign to agencies currently using Expedia TAAP to showcase MONDEE’s superior integration and cost‑efficiency.</t>
+          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference tools and automated commission tracking, directly addressing the gap left by Expedia TAAP’s recent rollout; pilot this with a select group of high‑volume agencies within 90 days.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Create a curated 'Granville Street Experience' package that bundles local attractions, dining, and walking tours, and partner with Vancouver businesses to offer exclusive discounts, leveraging the new pedestrian zone to drive bookings through MONDEE’s platform.</t>
+          <t>Develop a curated “Granville Street Experience” package on MONDEE that bundles accommodation, dining, and walking tours around Vancouver’s new pedestrian zone, and promote it through local tourism partners to capture the influx of visitors highlighted by Downtown Travel’s expansion.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Build a white‑label travel engine that can be embedded in partner agencies’ websites, and position it as a cost‑effective alternative to Priceline Partner Network’s engine, targeting agencies that rely on white‑label solutions for their clients.</t>
+          <t>Negotiate a white‑label integration with Priceline Partner Network’s engine to offer MONDEE’s travel solutions under partner brands, leveraging their existing distribution while differentiating with our AI‑driven itinerary personalization; target a pilot launch in the next fiscal quarter.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors, mirroring Expedia TAAP’s new tools, and offer a sandbox for agencies to integrate with MONDEE’s booking engine within 90 days. Include real‑time inventory, booking reference generation, and automated commission calculations to streamline agency operations.</t>
+          <t>Launch a dedicated back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s recent rollout, and pilot it with a select group of high‑volume agencies to validate integration ease and operational efficiency.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for travel advisors similar to Expedia TAAP Rewards, with instant points for each booking and quarterly bonus tiers, to incentivize partner loyalty and increase booking volume. Launch the program within 60 days and promote it through targeted webinars and agency newsletters.</t>
+          <t>Secure a partnership with a leading travel agency network to embed MONDEE’s white‑label travel engine, positioning it as a direct competitor to Priceline Partner Network’s quiet engine, and promote joint marketing to agencies.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine platform, inspired by Priceline Partner Network, that allows agencies to brand MONDEE’s booking interface and integrate it into their own sites, launching a pilot with 5 key agencies in 120 days. Provide API access and dedicated support to ensure seamless deployment and gather feedback for iterative improvement.</t>
+          <t>Introduce a tiered rewards program for advisors that offers commission boosts and exclusive benefits, directly countering Expedia TAAP’s rewards launch, and roll it out through a targeted email campaign to existing advisor partners.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a dedicated API integration layer that allows travel advisors to pull MONDEE’s itinerary optimization data directly into Expedia TAAP, positioning MONDEE as the preferred data partner for US travel advisors.</t>
+          <t>Launch a new travel‑advisor API that mirrors Expedia TAAP’s back‑office capabilities but adds AI‑driven itinerary optimization and real‑time local experience recommendations, and immediately pitch it to top US travel agencies to secure pilot contracts.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine tailored for US brands, mirroring Priceline Partner Network’s model, and target mid‑market travel agencies seeking a customizable booking platform.</t>
+          <t>Partner with Vancouver’s city council and local businesses to create a branded “Granville Street Walking Tour” mobile experience, bundling MONDEE’s booking engine with curated pedestrian routes and exclusive discounts, and launch a marketing campaign targeting US travelers visiting Vancouver.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism authority to create a pedestrian‑centric mobile guide app that highlights the new car‑free Granville Street, positioning MONDEE as the go‑to tech partner for sustainable urban travel experiences.</t>
+          <t>Develop a white‑label travel engine tailored for US brands, emphasizing advanced data analytics and personalization, and initiate outreach to Booking Holdings’ partners to position MONDEE as a competitive alternative to Priceline Partner Network.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a US‑focused travel advisor platform that mirrors Expedia TAAP, integrating a robust back‑office API and real‑time inventory tools to give advisors seamless booking and reporting capabilities.</t>
+          <t>Launch a US‑focused travel advisor platform with a behind‑the‑scenes engine and back‑office API, mirroring Expedia TAAP, and run a pilot with top advisors to refine the offering.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introduce a white‑label travel engine partnership program similar to Priceline Partner Network, allowing agencies to brand our booking engine while we handle inventory, pricing, and compliance.</t>
+          <t>Develop a white‑label travel engine that partners can embed, following Priceline Partner Network’s model, and target mid‑market OTAs and corporate travel platforms for rapid deployment.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deploy advanced data‑driven analytics dashboards for advisors, offering predictive pricing, demand forecasting, and personalized travel recommendations that differentiate us from generic competitor APIs.</t>
+          <t>Leverage the data from Expedia’s new back‑office API to create a predictive analytics dashboard for advisors, positioning MONDEE as the data‑driven partner for inventory, pricing, and demand insights.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API suite for travel advisors that includes real‑time booking reference tools and automated commission tracking, directly addressing the gap left by Expedia TAAP’s recent rollout; pilot this with a select group of high‑volume agencies within 90 days.</t>
+          <t>Deploy a new back‑office API for travel advisors that delivers instant booking reference generation and automated commission reconciliation, directly addressing Expedia TAAP’s recent launch and positioning MONDEE as the faster, more transparent alternative.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Develop a curated “Granville Street Experience” package on MONDEE that bundles accommodation, dining, and walking tours around Vancouver’s new pedestrian zone, and promote it through local tourism partners to capture the influx of visitors highlighted by Downtown Travel’s expansion.</t>
+          <t>Partner with Vancouver’s tourism board to launch a mobile itinerary feature that highlights the newly pedestrianized Granville Street, offering exclusive discounts and real‑time navigation, thereby capitalizing on the city’s expanded car‑free zone and attracting eco‑conscious travelers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label integration with Priceline Partner Network’s engine to offer MONDEE’s travel solutions under partner brands, leveraging their existing distribution while differentiating with our AI‑driven itinerary personalization; target a pilot launch in the next fiscal quarter.</t>
+          <t>Introduce a fully white‑label travel engine with advanced personalization and analytics, and target mid‑size agencies currently using Priceline Partner Network by offering a migration incentive and dedicated support, turning the Priceline announcement into a market‑entry opportunity.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Launch a dedicated back‑office API and suite of tools for travel advisors, mirroring Expedia TAAP’s recent rollout, and pilot it with a select group of high‑volume agencies to validate integration ease and operational efficiency.</t>
+          <t>Develop and launch a dedicated back‑office API suite for travel advisors, enabling real‑time booking, inventory management, and reporting, and pilot it with our top 10 agency partners within 90 days. This will position MONDEE as a full‑stack solution and directly compete with Expedia TAAP's new tools.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Secure a partnership with a leading travel agency network to embed MONDEE’s white‑label travel engine, positioning it as a direct competitor to Priceline Partner Network’s quiet engine, and promote joint marketing to agencies.</t>
+          <t>Introduce a tiered rewards program for agencies that unlocks higher commission rates and exclusive offers as booking volume increases, mirroring Expedia TAAP Rewards, and roll it out to our existing client base within 60 days. This will drive loyalty and volume while differentiating our value proposition.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for advisors that offers commission boosts and exclusive benefits, directly countering Expedia TAAP’s rewards launch, and roll it out through a targeted email campaign to existing advisor partners.</t>
+          <t>Negotiate a white‑label partnership with a leading travel engine such as Priceline Partner Network to broaden inventory and provide agencies with a seamless booking experience, and integrate it into MONDEE's platform by Q3. This will expand our market reach and reduce dependency on third‑party APIs.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Launch a new travel‑advisor API that mirrors Expedia TAAP’s back‑office capabilities but adds AI‑driven itinerary optimization and real‑time local experience recommendations, and immediately pitch it to top US travel agencies to secure pilot contracts.</t>
+          <t>Develop a US travel‑advisor‑focused API that offers real‑time inventory and dynamic pricing, and launch a pilot with top US agencies within 90 days to counter Expedia TAAP’s behind‑the‑scenes engine.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s city council and local businesses to create a branded “Granville Street Walking Tour” mobile experience, bundling MONDEE’s booking engine with curated pedestrian routes and exclusive discounts, and launch a marketing campaign targeting US travelers visiting Vancouver.</t>
+          <t>Expand MONDEE’s white‑label platform to include an AI recommendation engine and secure a partnership with a major US brand within 60 days, positioning MONDEE as the preferred tech partner against Priceline Partner Network’s white‑label travel engine.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine tailored for US brands, emphasizing advanced data analytics and personalization, and initiate outreach to Booking Holdings’ partners to position MONDEE as a competitive alternative to Priceline Partner Network.</t>
+          <t>Create a localized urban mobility package bundling bike‑share, public transit passes, and local attractions, and launch a marketing campaign targeting eco‑conscious travelers visiting Vancouver during the upcoming summer to capitalize on the car‑free Granville Street expansion.</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Launch a US‑focused travel advisor platform with a behind‑the‑scenes engine and back‑office API, mirroring Expedia TAAP, and run a pilot with top advisors to refine the offering.</t>
+          <t>Develop a US travel advisor platform mirroring Expedia TAAP, including a back‑office API and integrated tools to streamline booking workflows.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that partners can embed, following Priceline Partner Network’s model, and target mid‑market OTAs and corporate travel platforms for rapid deployment.</t>
+          <t>Launch a white‑label travel engine for partners, positioning MONDEE as a flexible alternative to Priceline’s engine, with customizable branding and pricing models.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leverage the data from Expedia’s new back‑office API to create a predictive analytics dashboard for advisors, positioning MONDEE as the data‑driven partner for inventory, pricing, and demand insights.</t>
+          <t>Integrate AI‑driven analytics into the advisor platform to provide real‑time market insights, giving advisors a competitive edge over Expedia’s new tools.</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deploy a new back‑office API for travel advisors that delivers instant booking reference generation and automated commission reconciliation, directly addressing Expedia TAAP’s recent launch and positioning MONDEE as the faster, more transparent alternative.</t>
+          <t>Develop and release a back‑office API and booking‑reference toolkit for travel advisors within 90 days, positioning MONDEE as a direct competitor to Expedia TAAP’s new offerings.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partner with Vancouver’s tourism board to launch a mobile itinerary feature that highlights the newly pedestrianized Granville Street, offering exclusive discounts and real‑time navigation, thereby capitalizing on the city’s expanded car‑free zone and attracting eco‑conscious travelers.</t>
+          <t>Form a white‑label partnership with a leading travel agency network to embed MONDEE’s engine, mirroring Priceline Partner Network’s model and expanding distribution channels.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Introduce a fully white‑label travel engine with advanced personalization and analytics, and target mid‑size agencies currently using Priceline Partner Network by offering a migration incentive and dedicated support, turning the Priceline announcement into a market‑entry opportunity.</t>
+          <t>Create a Vancouver‑centric travel package that includes exclusive access to the car‑free Granville Street event, leveraging the new pedestrian zone to attract eco‑conscious travelers.</t>
         </is>
       </c>
     </row>
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and launch a dedicated back‑office API suite for travel advisors, enabling real‑time booking, inventory management, and reporting, and pilot it with our top 10 agency partners within 90 days. This will position MONDEE as a full‑stack solution and directly compete with Expedia TAAP's new tools.</t>
+          <t>Build and launch a back‑office API suite for travel agencies, enabling them to manage bookings, references, and reporting directly from MONDEE’s platform, mirroring Expedia TAAP’s recent rollout, and provide comprehensive developer documentation and a sandbox environment to accelerate adoption.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies that unlocks higher commission rates and exclusive offers as booking volume increases, mirroring Expedia TAAP Rewards, and roll it out to our existing client base within 60 days. This will drive loyalty and volume while differentiating our value proposition.</t>
+          <t>Introduce a tiered rewards program for agencies that use MONDEE’s platform, offering commission boosts, co‑branded marketing assets, and exclusive access to premium features, to increase loyalty and volume in response to Expedia TAAP Rewards.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Negotiate a white‑label partnership with a leading travel engine such as Priceline Partner Network to broaden inventory and provide agencies with a seamless booking experience, and integrate it into MONDEE's platform by Q3. This will expand our market reach and reduce dependency on third‑party APIs.</t>
+          <t>Develop a white‑label travel engine that can be embedded by partner brands, leveraging MONDEE’s existing booking infrastructure, to compete with Priceline Partner Network’s quiet engine and open new revenue streams.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2629,92 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Downtown Travel News</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Downtown+Travel%22+when:1d&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.mychesco.com/a/news/regional/doylestown-street-closures-could-disrupt-downtown-travel-for-months/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:20:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Downtown Travel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Downtown Travel (Brand)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Doylestown Street Closures Could Disrupt Downtown Travel for Months - MyChesCo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Alec Robson</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street.
+Crews will close and detour one section of roadway at a time to minimize disruptions.
+Closures on State Street will occur between:
+Closures on Main Street will occur between State Street and Court Street. Drivers will be directed to use State Street and Court Street.
+Local access will be maintained throughout construction. Drivers should plan extra time when traveling through downtown Doylestown because backups and delays are expected. Seek alternate routes whenever possible, especially during business hours.
+The construction schedule is weather dependent and may change if conditions are unfavorable.
+With work expected to continue through early December, motorists should anticipate changing traffic patterns as different sections of State Street and Main Street are closed throughout the project.
+Do not let downtown road closures catch you by surprise. Check the latest road restrictions, detours and traffic alerts at the MyChesCo Traffic Center before heading out: https://www.mychesco.com/traffic/
+Support the local news that supports Chester County. MyChesCo delivers reliable, fact-based reporting and essential community resources—free for everyone. If you value that, click here to become a patron today.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-30 18:04:04</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street. Crews will close and detour one section of roadway at a time to minimize disruptions.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Tier 4 - Low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/News_Dashboard/data/raw_news_database_Mondee.xlsx
+++ b/News_Dashboard/data/raw_news_database_Mondee.xlsx
@@ -2691,11 +2691,31 @@
           <t>2026-07-30 18:04:04</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Downtown Travel executed general industry news movement impacting Mondee market segment</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Standard market activity by Downtown Travel. No direct action required for Mondee.</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>DOYLESTOWN, PA — Drivers should prepare for months of daytime and overnight road closures in downtown Doylestown as PECO Energy begins utility construction affecting sections of State Street and Main Street. Crews will close and detour one section of roadway at a time to minimize disruptions.</t>
@@ -2707,11 +2727,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>Tier 4 - Low</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Overview</t>
         </is>
       </c>
     </row>
@@ -2932,17 +2957,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Develop a US travel‑advisor‑focused API that offers real‑time inventory and dynamic pricing, and launch a pilot with top US agencies within 90 days to counter Expedia TAAP’s behind‑the‑scenes engine.</t>
+          <t>Market conditions are currently stable.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Expand MONDEE’s white‑label platform to include an AI recommendation engine and secure a partnership with a major US brand within 60 days, positioning MONDEE as the preferred tech partner against Priceline Partner Network’s white‑label travel engine.</t>
+          <t>No high-priority competitor moves detected in this timeframe.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Create a localized urban mobility package bundling bike‑share, public transit passes, and local attractions, and launch a marketing campaign targeting eco‑conscious travelers visiting Vancouver during the upcoming summer to capitalize on the car‑free Granville Street expansion.</t>
+          <t>Continue tracking standard sector intelligence.</t>
         </is>
       </c>
     </row>
@@ -2986,17 +3011,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a US travel advisor platform mirroring Expedia TAAP, including a back‑office API and integrated tools to streamline booking workflows.</t>
+          <t>No competitor product launches or API releases cataloged.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launch a white‑label travel engine for partners, positioning MONDEE as a flexible alternative to Priceline’s engine, with customizable branding and pricing models.</t>
+          <t>Digital feature velocity remains normal.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Integrate AI‑driven analytics into the advisor platform to provide real‑time market insights, giving advisors a competitive edge over Expedia’s new tools.</t>
+          <t>Continue monitoring competitor release notes.</t>
         </is>
       </c>
     </row>
@@ -3013,17 +3038,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop and release a back‑office API and booking‑reference toolkit for travel advisors within 90 days, positioning MONDEE as a direct competitor to Expedia TAAP’s new offerings.</t>
+          <t>Market conditions are currently stable.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Form a white‑label partnership with a leading travel agency network to embed MONDEE’s engine, mirroring Priceline Partner Network’s model and expanding distribution channels.</t>
+          <t>No high-priority competitor moves detected in this timeframe.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Create a Vancouver‑centric travel package that includes exclusive access to the car‑free Granville Street event, leveraging the new pedestrian zone to attract eco‑conscious travelers.</t>
+          <t>Continue tracking standard sector intelligence.</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3092,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Build and launch a back‑office API suite for travel agencies, enabling them to manage bookings, references, and reporting directly from MONDEE’s platform, mirroring Expedia TAAP’s recent rollout, and provide comprehensive developer documentation and a sandbox environment to accelerate adoption.</t>
+          <t>No competitor product launches or API releases cataloged.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introduce a tiered rewards program for agencies that use MONDEE’s platform, offering commission boosts, co‑branded marketing assets, and exclusive access to premium features, to increase loyalty and volume in response to Expedia TAAP Rewards.</t>
+          <t>Digital feature velocity remains normal.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Develop a white‑label travel engine that can be embedded by partner brands, leveraging MONDEE’s existing booking infrastructure, to compete with Priceline Partner Network’s quiet engine and open new revenue streams.</t>
+          <t>Continue monitoring competitor release notes.</t>
         </is>
       </c>
     </row>
